--- a/public/downloads/DheerNitrogenase2025.xlsx
+++ b/public/downloads/DheerNitrogenase2025.xlsx
@@ -1581,16 +1581,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2532218405695289</v>
+        <v>0.2310153036050338</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4949450402258823</v>
+        <v>0.4912439507317997</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.325541361374776</v>
+        <v>0.321100053981877</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4094145436936897</v>
+        <v>-0.2974938713358739</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -4497,16 +4497,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5996340852949175</v>
+        <v>-0.7749182537683055</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4227712916866693</v>
+        <v>0.5104133759233633</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4950165392212921</v>
+        <v>0.4599597055266145</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1211470705244096</v>
+        <v>-0.07075446401915997</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -5254,7 +5254,7 @@
         <v>0.3269604097059092</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08853505837392277</v>
+        <v>0.07845653707287284</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -8227,13 +8227,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6652622719787035</v>
+        <v>-0.6151304715234538</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.362394791383581</v>
+        <v>0.3373288911559562</v>
       </c>
       <c r="Q3" s="4">
         <v>0.4760521792207975</v>
@@ -8985,13 +8985,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.459085879488664</v>
+        <v>0.488578774581548</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5452334895956341</v>
+        <v>0.5288636877853037</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4352042563870337</v>
+        <v>0.4575151955918602</v>
       </c>
       <c r="K4" s="4">
         <v>30.15117157974299</v>
@@ -9035,13 +9035,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5361988430657819</v>
+        <v>0.542995909005432</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2495147164335002</v>
+        <v>0.2455760833761629</v>
       </c>
       <c r="J5" s="4">
-        <v>0.8003366325809547</v>
+        <v>0.8108396540671878</v>
       </c>
       <c r="K5" s="4">
         <v>26.81531872008065</v>
@@ -9138,7 +9138,7 @@
         <v>2.267626075741666</v>
       </c>
       <c r="I7" s="4">
-        <v>0.8120344792808124</v>
+        <v>0.8060315300382462</v>
       </c>
       <c r="J7" s="4">
         <v>1.952625682969133</v>
@@ -9185,13 +9185,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.8705277722657419</v>
+        <v>0.8697053079337235</v>
       </c>
       <c r="I8" s="4">
-        <v>0.5998143999191454</v>
+        <v>0.5985807034211178</v>
       </c>
       <c r="J8" s="4">
-        <v>0.7961532349388195</v>
+        <v>0.7952113487960356</v>
       </c>
       <c r="K8" s="4">
         <v>25.23242630385481</v>
@@ -9291,7 +9291,7 @@
         <v>0.4205293144340756</v>
       </c>
       <c r="J10" s="4">
-        <v>0.574924520946279</v>
+        <v>0.5738511286075175</v>
       </c>
       <c r="K10" s="4">
         <v>46.80272108843531</v>
@@ -9385,13 +9385,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.5764096890273644</v>
+        <v>0.5958857077466299</v>
       </c>
       <c r="I12" s="4">
-        <v>0.4274015268176631</v>
+        <v>0.4176635174580304</v>
       </c>
       <c r="J12" s="4">
-        <v>0.6043752011200166</v>
+        <v>0.6249016742569435</v>
       </c>
       <c r="K12" s="4">
         <v>35.47933988410175</v>
@@ -9438,10 +9438,10 @@
         <v>1.104516110129901</v>
       </c>
       <c r="I13" s="4">
-        <v>0.6825876995507527</v>
+        <v>0.679788110300461</v>
       </c>
       <c r="J13" s="4">
-        <v>0.9547344255542948</v>
+        <v>0.9599216499660785</v>
       </c>
       <c r="K13" s="4">
         <v>26.08276643990933</v>
@@ -9635,13 +9635,13 @@
         <v>9.25925925925926</v>
       </c>
       <c r="H17" s="4">
-        <v>1.144304116443374</v>
+        <v>1.138733916392791</v>
       </c>
       <c r="I17" s="4">
         <v>0.6936535348153948</v>
       </c>
       <c r="J17" s="4">
-        <v>1.087687528549452</v>
+        <v>1.089544261899646</v>
       </c>
       <c r="K17" s="4">
         <v>42.4092970521542</v>
@@ -12048,16 +12048,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2192067045000044</v>
+        <v>-0.07544972808594252</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2139470079776193</v>
+        <v>0.3466650358955974</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.382588789587503</v>
+        <v>0.3236575030703136</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -12796,16 +12796,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3844752949449571</v>
+        <v>-0.4553706899770305</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2773084563033525</v>
+        <v>0.3078952530317783</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3906085373215729</v>
+        <v>0.3764294583151582</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8400408846113236</v>
+        <v>-0.7860143414282277</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -14267,7 +14267,7 @@
         <v>0.4756962346303292</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2233123365628921</v>
+        <v>0.2125070279262729</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
